--- a/kapremont/output/Квитанции_квартальные_Магистральная-2_шаблон.xlsx
+++ b/kapremont/output/Квитанции_квартальные_Магистральная-2_шаблон.xlsx
@@ -1025,7 +1025,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ячейки на бирюзовом фоне — для ввода. Всё остальное в книге считается формулами от них; квитанции и письма пересчитаются сами.</t>
+          <t>Залитые ячейки — для ввода. Всё остальное в книге считается формулами от них; квитанции и письма пересчитаются сами.</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Начислено за месяц, руб.</t>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>«от Председателя … Яворсюк Елены Викторовны»</t>
+          <t>«от Председателя … Ивановой Марии Петровны»</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
     </row>
-    <row r="40" ht="44" customHeight="1">
+    <row r="40" ht="52" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Получатель платежа</t>

--- a/kapremont/output/Квитанции_квартальные_Магистральная-2_шаблон.xlsx
+++ b/kapremont/output/Квитанции_квартальные_Магистральная-2_шаблон.xlsx
@@ -1751,7 +1751,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="77">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$34)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$34)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="77" t="n"/>
@@ -32150,7 +32150,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -32239,7 +32239,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -32847,7 +32847,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -32936,7 +32936,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -33544,7 +33544,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -33633,7 +33633,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -34241,7 +34241,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -34330,7 +34330,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -35015,7 +35015,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="77">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="77" t="n"/>
@@ -35256,7 +35256,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="77">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="77" t="n"/>
@@ -35497,7 +35497,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="77">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="77" t="n"/>
